--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_48.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4469246.640635231</v>
+        <v>4505604.686942446</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117102065</v>
+        <v>603.5370117078833</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117102065</v>
+        <v>603.5370117078833</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T2" t="n">
         <v>184.8805867536895</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>138.8829806321345</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>211.5126764242681</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>374</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>211.8824232220852</v>
       </c>
       <c r="S6" t="n">
         <v>62.48881128536601</v>
@@ -1027,13 +1027,13 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V6" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>334.4909338603296</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1146,10 +1146,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1219,7 +1219,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.361097301488838</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>128.9709564352693</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1386,7 +1386,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1106633827815</v>
+        <v>328.5712507480957</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1450,7 +1450,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>21.67209722191262</v>
@@ -1459,10 +1459,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608469</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>226.7834941523314</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
@@ -1507,10 +1507,10 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
@@ -1696,7 +1696,7 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H15" t="n">
         <v>4.021973978873973</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>180.333570877285</v>
+        <v>353.9253867592582</v>
       </c>
       <c r="S15" t="n">
         <v>131.8202263797057</v>
@@ -1744,7 +1744,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>98.86273944538755</v>
@@ -1793,7 +1793,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
         <v>155.2579933044718</v>
@@ -1811,7 +1811,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H17" t="n">
         <v>72.84688483418068</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T17" t="n">
         <v>259.6218731858503</v>
@@ -1908,7 +1908,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>190.7780200481207</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>195.2639131038855</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T18" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2039,16 +2039,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S19" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158.5198244189524</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>180.333570877285</v>
@@ -2221,10 +2221,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273608</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2270,7 +2270,7 @@
         <v>102.3923982877958</v>
       </c>
       <c r="N22" t="n">
-        <v>155.2579933044718</v>
+        <v>154.4197474548741</v>
       </c>
       <c r="O22" t="n">
         <v>231.765039488851</v>
@@ -2285,7 +2285,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>135.063180218145</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.99961134672543</v>
+        <v>177.5914272286986</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2510,19 +2510,19 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O25" t="n">
-        <v>231.765039488851</v>
+        <v>230.9267936392535</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H26" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2635,19 +2635,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>195.2639131038857</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2680,13 +2680,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2695,10 +2695,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,16 +2750,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
@@ -2878,7 +2878,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>3.99961134672543</v>
@@ -2887,7 +2887,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I30" t="n">
-        <v>94.9632677726258</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
@@ -2926,16 +2926,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2993,10 +2993,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038858</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
@@ -3163,13 +3163,13 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
-        <v>267.1024830734933</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -3282,7 +3282,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3349,10 +3349,10 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>116.6353649945384</v>
       </c>
       <c r="F36" t="n">
-        <v>192.2280582198502</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
         <v>3.999611346725456</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
@@ -3406,7 +3406,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>78.39139276613435</v>
@@ -3516,7 +3516,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>142.3350019731772</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>40.09991244551929</v>
@@ -3586,10 +3586,10 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
         <v>3.99961134672543</v>
@@ -3625,7 +3625,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499106</v>
       </c>
       <c r="S39" t="n">
         <v>131.8202263797057</v>
@@ -3637,16 +3637,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>173.3546605387602</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3707,7 +3707,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090247613</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>237.1483725282997</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -3880,10 +3880,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y42" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3944,7 +3944,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>237.1483725282993</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>173.5918158819731</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4117,10 +4117,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4178,10 +4178,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
@@ -4324,7 +4324,7 @@
         <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>263.0661931588676</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
         <v>327.128108133742</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.92</v>
+        <v>862.620151643509</v>
       </c>
       <c r="C3" t="n">
-        <v>29.92</v>
+        <v>862.620151643509</v>
       </c>
       <c r="D3" t="n">
-        <v>29.92</v>
+        <v>862.620151643509</v>
       </c>
       <c r="E3" t="n">
-        <v>29.92</v>
+        <v>516.4867201062234</v>
       </c>
       <c r="F3" t="n">
-        <v>29.92</v>
+        <v>173.4198086538225</v>
       </c>
       <c r="G3" t="n">
-        <v>29.92</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>29.92</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="J3" t="n">
-        <v>174.3973709300159</v>
+        <v>177.6113405614803</v>
       </c>
       <c r="K3" t="n">
-        <v>398.6635894772295</v>
+        <v>401.8775591086939</v>
       </c>
       <c r="L3" t="n">
-        <v>717.174568996958</v>
+        <v>720.3885386284223</v>
       </c>
       <c r="M3" t="n">
-        <v>858.2892107398172</v>
+        <v>861.5031803712816</v>
       </c>
       <c r="N3" t="n">
-        <v>1048.06018421531</v>
+        <v>1051.274153846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.994549492757</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.786030368536</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1492.786030368536</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1115.008252590758</v>
+        <v>1360.997993968056</v>
       </c>
       <c r="S3" t="n">
-        <v>1051.888241191398</v>
+        <v>1297.877982568697</v>
       </c>
       <c r="T3" t="n">
-        <v>838.2390730860769</v>
+        <v>1293.359351798195</v>
       </c>
       <c r="U3" t="n">
-        <v>460.4612953082991</v>
+        <v>1293.161446951808</v>
       </c>
       <c r="V3" t="n">
-        <v>82.68351753052127</v>
+        <v>915.3836691740303</v>
       </c>
       <c r="W3" t="n">
-        <v>49.98337317715914</v>
+        <v>882.6835248206681</v>
       </c>
       <c r="X3" t="n">
-        <v>29.92</v>
+        <v>862.620151643509</v>
       </c>
       <c r="Y3" t="n">
-        <v>29.92</v>
+        <v>862.620151643509</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>727.7159997688324</v>
+        <v>820.5787742170542</v>
       </c>
       <c r="C4" t="n">
-        <v>853.7180055872682</v>
+        <v>820.5787742170542</v>
       </c>
       <c r="D4" t="n">
-        <v>853.7180055872682</v>
+        <v>933.8979183420543</v>
       </c>
       <c r="E4" t="n">
-        <v>853.7180055872682</v>
+        <v>933.8979183420543</v>
       </c>
       <c r="F4" t="n">
-        <v>853.7180055872682</v>
+        <v>1058.25889093399</v>
       </c>
       <c r="G4" t="n">
-        <v>853.7180055872682</v>
+        <v>1211.847551902842</v>
       </c>
       <c r="H4" t="n">
-        <v>1024.853581566338</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.462556240126</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="K4" t="n">
         <v>1382.983127881912</v>
@@ -4509,22 +4509,22 @@
         <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>205.9728975990155</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>205.9728975990155</v>
+        <v>75.66903370191284</v>
       </c>
       <c r="V4" t="n">
-        <v>404.7942904849615</v>
+        <v>274.4904265878588</v>
       </c>
       <c r="W4" t="n">
-        <v>576.6852087446389</v>
+        <v>446.3813448475362</v>
       </c>
       <c r="X4" t="n">
-        <v>727.7159997688324</v>
+        <v>597.4121358717297</v>
       </c>
       <c r="Y4" t="n">
-        <v>727.7159997688324</v>
+        <v>708.821436550762</v>
       </c>
     </row>
     <row r="5">
@@ -4561,22 +4561,22 @@
         <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>263.0661931588676</v>
       </c>
       <c r="L5" t="n">
-        <v>770.4399999999999</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>1140.7</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1132.224462223578</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1069.104450824218</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1064.585820053716</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>686.8080422759385</v>
       </c>
       <c r="V6" t="n">
-        <v>765.6307811168861</v>
+        <v>672.1508026885444</v>
       </c>
       <c r="W6" t="n">
-        <v>427.761150954937</v>
+        <v>639.4506583351823</v>
       </c>
       <c r="X6" t="n">
-        <v>407.6977777777778</v>
+        <v>619.3872851580231</v>
       </c>
       <c r="Y6" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>496.5679514324192</v>
+        <v>653.4527687319187</v>
       </c>
       <c r="C7" t="n">
-        <v>622.5699572508551</v>
+        <v>779.4547745503545</v>
       </c>
       <c r="D7" t="n">
-        <v>735.8891013758551</v>
+        <v>779.4547745503545</v>
       </c>
       <c r="E7" t="n">
-        <v>853.7180055872682</v>
+        <v>779.4547745503545</v>
       </c>
       <c r="F7" t="n">
-        <v>853.7180055872682</v>
+        <v>779.4547745503545</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>779.4547745503545</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>950.5903505294242</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U7" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="V7" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="W7" t="n">
-        <v>259.1973975316665</v>
+        <v>390.6646400414331</v>
       </c>
       <c r="X7" t="n">
-        <v>410.22818855586</v>
+        <v>541.6954310656266</v>
       </c>
       <c r="Y7" t="n">
-        <v>496.5679514324192</v>
+        <v>541.6954310656266</v>
       </c>
     </row>
     <row r="8">
@@ -4789,7 +4789,7 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4804,7 +4804,7 @@
         <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>886.1402453266331</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N8" t="n">
         <v>1067.648108133742</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1092.253026833469</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C9" t="n">
-        <v>727.505640524864</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="D9" t="n">
-        <v>376.0534315372855</v>
+        <v>724.5355927891701</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>378.4021612518846</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>35.33524979948368</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1362.512336999577</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1227.510330967633</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1164.390319568273</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1159.871688797771</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>1159.673783951385</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>1145.016544363991</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>1112.316400010629</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X9" t="n">
-        <v>1092.253026833469</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y9" t="n">
-        <v>1092.253026833469</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>460.8081946749797</v>
+        <v>330.5310594480478</v>
       </c>
       <c r="C10" t="n">
-        <v>586.8102004934156</v>
+        <v>330.5310594480478</v>
       </c>
       <c r="D10" t="n">
-        <v>700.1293446184156</v>
+        <v>443.8502035730479</v>
       </c>
       <c r="E10" t="n">
-        <v>700.1293446184156</v>
+        <v>561.6791077844609</v>
       </c>
       <c r="F10" t="n">
-        <v>700.1293446184156</v>
+        <v>686.0400803763964</v>
       </c>
       <c r="G10" t="n">
-        <v>853.7180055872682</v>
+        <v>686.0400803763964</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>686.0400803763964</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>912.6490550501842</v>
       </c>
       <c r="J10" t="n">
         <v>1251.462556240126</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>48.78783454789968</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>237.6415563296554</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U10" t="n">
-        <v>237.6415563296554</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="V10" t="n">
-        <v>237.6415563296554</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="W10" t="n">
-        <v>237.6415563296554</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="X10" t="n">
-        <v>237.6415563296554</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="Y10" t="n">
-        <v>349.0508570086876</v>
+        <v>218.7737217817557</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D11" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H11" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
@@ -5038,10 +5038,10 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>1418.446838088717</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M11" t="n">
-        <v>2060.956838088718</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5065,19 +5065,19 @@
         <v>2189.982954384821</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.6952769985969</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C12" t="n">
-        <v>452.1903149324158</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D12" t="n">
-        <v>424.9805301872616</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0895228924003</v>
+        <v>902.677215702474</v>
       </c>
       <c r="F12" t="n">
-        <v>60.0226114399994</v>
+        <v>559.6103042500731</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866058</v>
+        <v>231.32786854631</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.535205884734</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W12" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X12" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y12" t="n">
-        <v>556.8938190655934</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N13" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O13" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R13" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5275,16 +5275,16 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L14" t="n">
-        <v>991.9887866314309</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1634.498786631431</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="O14" t="n">
-        <v>2399.40799366138</v>
+        <v>1953.49</v>
       </c>
       <c r="P14" t="n">
         <v>2596</v>
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.180125483445</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C15" t="n">
         <v>776.43273917484</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G15" t="n">
         <v>55.98259997866058</v>
@@ -5372,28 +5372,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R15" t="n">
-        <v>2062.032218270268</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1753.535205884733</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V15" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118091</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="16">
@@ -5436,22 +5436,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O16" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R16" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5494,7 +5494,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F17" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G17" t="n">
         <v>125.5027119537179</v>
@@ -5506,16 +5506,16 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L17" t="n">
-        <v>1418.446838088717</v>
+        <v>1844.448527309012</v>
       </c>
       <c r="M17" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="N17" t="n">
         <v>2238.277892278425</v>
@@ -5533,22 +5533,22 @@
         <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X17" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y17" t="n">
         <v>759.2809169713448</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668.0405455662462</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C18" t="n">
-        <v>303.2931592576409</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D18" t="n">
-        <v>276.0833745124867</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E18" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G18" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5615,22 +5615,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U18" t="n">
         <v>1766.721857646244</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W18" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X18" t="n">
-        <v>1135.664736891964</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y18" t="n">
-        <v>732.2390876332428</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="19">
@@ -5682,13 +5682,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R19" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5743,19 +5743,19 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L20" t="n">
-        <v>1418.446838088717</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="M20" t="n">
-        <v>2060.956838088718</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="N20" t="n">
-        <v>2238.277892278425</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O20" t="n">
         <v>2399.40799366138</v>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C21" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D21" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E21" t="n">
         <v>78.84709864997603</v>
@@ -5843,31 +5843,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U21" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>1380.484385266361</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y21" t="n">
-        <v>1301.301160250064</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="22">
@@ -5913,19 +5913,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D23" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E23" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G23" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5983,49 +5983,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L23" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M23" t="n">
-        <v>1595.767892278425</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N23" t="n">
-        <v>2238.277892278425</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O23" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1237.102618183067</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.675163417264</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D24" t="n">
-        <v>749.2229544296858</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>902.6772157024742</v>
       </c>
       <c r="F24" t="n">
-        <v>60.0226114399994</v>
+        <v>559.6103042500733</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866058</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6080,31 +6080,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R24" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S24" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>1380.484385266361</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>1301.301160250064</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6153,16 +6153,16 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
         <v>51.92</v>
@@ -6220,16 +6220,16 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L26" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M26" t="n">
-        <v>2060.956838088718</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O26" t="n">
         <v>2399.40799366138</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>992.2829698086707</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C27" t="n">
-        <v>627.5355835000653</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D27" t="n">
-        <v>276.0833745124868</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E27" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F27" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6326,7 +6326,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U27" t="n">
         <v>1766.721857646244</v>
@@ -6338,10 +6338,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y27" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D29" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G29" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6454,16 +6454,16 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M29" t="n">
-        <v>2060.956838088718</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N29" t="n">
         <v>2238.277892278425</v>
@@ -6478,28 +6478,28 @@
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S29" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W29" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>588.6177696982188</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C30" t="n">
-        <v>548.1128076320377</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D30" t="n">
-        <v>520.9030228868836</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E30" t="n">
-        <v>499.0120155920224</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
-        <v>155.9451041396214</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G30" t="n">
-        <v>151.9050926782826</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H30" t="n">
-        <v>147.842492699622</v>
+        <v>51.92</v>
       </c>
       <c r="I30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>831.8608897566517</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X30" t="n">
-        <v>731.9995367815127</v>
+        <v>811.4223126495401</v>
       </c>
       <c r="Y30" t="n">
-        <v>652.8163117652153</v>
+        <v>407.9966633908185</v>
       </c>
     </row>
     <row r="31">
@@ -6636,7 +6636,7 @@
         <v>463.4700425881595</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,37 +6667,37 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L32" t="n">
-        <v>1376.091327711023</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M32" t="n">
         <v>1595.767892278425</v>
@@ -6715,28 +6715,28 @@
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.4528527561725</v>
+        <v>668.0405455662465</v>
       </c>
       <c r="C33" t="n">
-        <v>127.9478906899915</v>
+        <v>303.2931592576411</v>
       </c>
       <c r="D33" t="n">
-        <v>100.7381059448373</v>
+        <v>276.0833745124869</v>
       </c>
       <c r="E33" t="n">
         <v>78.84709864997603</v>
@@ -6806,16 +6806,16 @@
         <v>1766.721857646244</v>
       </c>
       <c r="V33" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.6513948231691</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="34">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
@@ -6952,28 +6952,28 @@
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>992.2829698086708</v>
+        <v>588.6177696982188</v>
       </c>
       <c r="C36" t="n">
-        <v>627.5355835000655</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D36" t="n">
-        <v>600.3257987549114</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E36" t="n">
-        <v>254.1923672176259</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
         <v>60.02261143999941</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V36" t="n">
-        <v>1348.024214018445</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867104</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X36" t="n">
-        <v>1135.664736891965</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y36" t="n">
-        <v>1056.481511875667</v>
+        <v>652.8163117652153</v>
       </c>
     </row>
     <row r="37">
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C38" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D38" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E38" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G38" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H38" t="n">
         <v>51.92</v>
@@ -7165,52 +7165,52 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>1418.446838088717</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M38" t="n">
-        <v>2060.956838088718</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N38" t="n">
-        <v>2238.277892278425</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O38" t="n">
-        <v>2399.40799366138</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P38" t="n">
-        <v>2596</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W38" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X38" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>816.937701241021</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C39" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D39" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
         <v>60.0226114399994</v>
@@ -7268,28 +7268,28 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R39" t="n">
-        <v>1982.60944240224</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S39" t="n">
-        <v>1849.457698584356</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T39" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U39" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V39" t="n">
-        <v>1592.843862392842</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W39" t="n">
-        <v>1480.3457382415</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X39" t="n">
-        <v>1380.484385266361</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y39" t="n">
-        <v>1205.378667550442</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611905</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024183</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405794</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468627</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605524</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111735</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645593</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881977</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949745064</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7414,7 +7414,7 @@
         <v>1166.141587033441</v>
       </c>
       <c r="N41" t="n">
-        <v>1170.453074689115</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
         <v>1812.963074689115</v>
@@ -7426,28 +7426,28 @@
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>816.9377012410212</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D42" t="n">
         <v>424.9805301872615</v>
@@ -7523,10 +7523,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X42" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y42" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080177</v>
       </c>
     </row>
     <row r="43">
@@ -7566,25 +7566,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,40 +7615,40 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D44" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H44" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>1844.448527309012</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>2238.277892278425</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N44" t="n">
         <v>2238.277892278425</v>
@@ -7663,28 +7663,28 @@
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W44" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>816.9377012410212</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C45" t="n">
-        <v>452.1903149324157</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D45" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E45" t="n">
-        <v>78.84709864997603</v>
+        <v>902.6772157024742</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>559.6103042500733</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866058</v>
+        <v>555.5702927887345</v>
       </c>
       <c r="H45" t="n">
-        <v>51.92</v>
+        <v>227.2652685676496</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7760,7 +7760,7 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1459.907161134389</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y45" t="n">
         <v>1056.481511875667</v>
@@ -7821,7 +7821,7 @@
         <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7967,10 +7967,10 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>183.3412755627362</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
@@ -8204,16 +8204,16 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748743</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>704.292876848652</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>655.6021670241489</v>
       </c>
       <c r="N8" t="n">
-        <v>587.423942175285</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8681,13 +8681,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>409.6042294964216</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8918,19 +8918,19 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N14" t="n">
-        <v>840.3699380391354</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>377.6899601296239</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q14" t="n">
         <v>23.48346824708341</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L17" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>699.241868512898</v>
       </c>
       <c r="N17" t="n">
-        <v>409.6042294964216</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9386,22 +9386,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>342.3308260703579</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
-        <v>409.6042294964216</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9626,25 +9626,25 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>480.5466050990546</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>234.8470915832563</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,19 +9863,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,16 +10334,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427137</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>523.3299489149077</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
         <v>879.4920535472222</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.48346824708341</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11057,10 +11057,10 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>234.8470915832563</v>
+        <v>721.0894134186553</v>
       </c>
       <c r="O41" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>230.4920535472222</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24128,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.8382458495976266</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24368,7 +24368,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24851,10 +24851,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.838245849559641</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26302,10 +26302,10 @@
         <v>1511228.306918645</v>
       </c>
       <c r="M2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918644</v>
       </c>
       <c r="N2" t="n">
-        <v>1511228.306918646</v>
+        <v>1511228.306918647</v>
       </c>
       <c r="O2" t="n">
         <v>1511228.306918645</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658208</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604934</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>644099.1137323488</v>
+        <v>650600.4786653258</v>
       </c>
       <c r="C6" t="n">
-        <v>877206.0359198371</v>
+        <v>883707.400852814</v>
       </c>
       <c r="D6" t="n">
-        <v>879217.6833356611</v>
+        <v>885719.048268638</v>
       </c>
       <c r="E6" t="n">
-        <v>357794.7781224713</v>
+        <v>364257.7692528252</v>
       </c>
       <c r="F6" t="n">
-        <v>949030.8409406937</v>
+        <v>955493.8320710483</v>
       </c>
       <c r="G6" t="n">
-        <v>950719.2304623461</v>
+        <v>957182.2215926999</v>
       </c>
       <c r="H6" t="n">
-        <v>952409.9633723089</v>
+        <v>958872.9545026629</v>
       </c>
       <c r="I6" t="n">
-        <v>954103.0565728563</v>
+        <v>960566.0477032106</v>
       </c>
       <c r="J6" t="n">
-        <v>567350.5271877811</v>
+        <v>573813.5183181355</v>
       </c>
       <c r="K6" t="n">
-        <v>957496.3925666148</v>
+        <v>963959.383696969</v>
       </c>
       <c r="L6" t="n">
-        <v>959196.6702889578</v>
+        <v>965659.6614193122</v>
       </c>
       <c r="M6" t="n">
-        <v>864099.3781689262</v>
+        <v>870562.3692992793</v>
       </c>
       <c r="N6" t="n">
-        <v>962604.5342596903</v>
+        <v>969067.5253900451</v>
       </c>
       <c r="O6" t="n">
-        <v>707512.1568581519</v>
+        <v>713975.147988506</v>
       </c>
       <c r="P6" t="n">
-        <v>966022.2645097356</v>
+        <v>972485.2556400899</v>
       </c>
     </row>
   </sheetData>
@@ -26990,16 +26990,16 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>321</v>
+      </c>
+      <c r="K2" t="n">
         <v>-0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>321</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,13 +27521,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>186.6371590164777</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
@@ -27560,16 +27560,16 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>192.9607680385288</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>40.51066719152016</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D4" t="n">
         <v>400</v>
-      </c>
-      <c r="D4" t="n">
-        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,10 +27645,10 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
-        <v>387.0698745628887</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>197.15950364102</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27770,7 +27770,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,7 +27797,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>321.7695627495393</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,13 +27806,13 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
+        <v>26.1959257979226</v>
+      </c>
+      <c r="V6" t="n">
         <v>400</v>
       </c>
-      <c r="V6" t="n">
-        <v>40.51066719152016</v>
-      </c>
       <c r="W6" t="n">
-        <v>97.8822090494989</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
@@ -27849,16 +27849,16 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>237.6608315772878</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>374.6772345429565</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -27998,7 +27998,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>325.5201396486123</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>204.211515004954</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.10257280615369</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28068,28 +28068,28 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>364.5006446893012</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>378.2264230282715</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28229,7 +28229,7 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>321</v>
@@ -28238,10 +28238,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="I12" t="n">
         <v>191.6509141932353</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,10 +28286,10 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -28475,7 +28475,7 @@
         <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28508,7 +28508,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="S15" t="n">
         <v>321</v>
@@ -28523,7 +28523,7 @@
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>321</v>
@@ -28669,7 +28669,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
@@ -28687,7 +28687,7 @@
         <v>321</v>
       </c>
       <c r="Y17" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18">
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28757,7 +28757,7 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>226.0367322273742</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -29000,10 +29000,10 @@
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,22 +29174,22 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="H24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>191.6509141932353</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>96.76634561233286</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29414,10 +29414,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29474,10 +29474,10 @@
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
@@ -29657,7 +29657,7 @@
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29666,7 +29666,7 @@
         <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>96.68764642060954</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29705,16 +29705,16 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29942,13 +29942,13 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30128,10 +30128,10 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="F36" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
@@ -30185,7 +30185,7 @@
         <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>321</v>
@@ -30295,7 +30295,7 @@
         <v>321</v>
       </c>
       <c r="H38" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I38" t="n">
         <v>96.76634561233286</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
         <v>321</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C39" t="n">
         <v>321</v>
@@ -30365,10 +30365,10 @@
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30404,7 +30404,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="S39" t="n">
         <v>321</v>
@@ -30416,16 +30416,16 @@
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321</v>
+        <v>321.0000000000385</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,13 +30593,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -30659,10 +30659,10 @@
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,28 +30830,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147.4081841180273</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126223</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30896,10 +30896,10 @@
         <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46">
@@ -34746,10 +34746,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>235.5012052109774</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>248.0502805878618</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34877,34 +34877,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H4" t="n">
         <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>3.798404629106074</v>
@@ -34931,10 +34931,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>177.8312096959753</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>46.21114515344731</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,16 +34983,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="L5" t="n">
-        <v>373.9999999999999</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>300.2102102361032</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -35135,16 +35135,16 @@
         <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>66.55878579323509</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>190.7613351330866</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>87.21188169349418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35226,10 +35226,10 @@
         <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
+        <v>183.3412755627362</v>
+      </c>
+      <c r="N8" t="n">
         <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>183.3412755627362</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35354,28 +35354,28 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>342.2358597878197</v>
       </c>
       <c r="K10" t="n">
         <v>132.8490622644307</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>19.0584187352522</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>190.7613351330866</v>
@@ -35420,7 +35420,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35460,13 +35460,13 @@
         <v>649</v>
       </c>
       <c r="L11" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>179.1121759491994</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35697,19 +35697,19 @@
         <v>649</v>
       </c>
       <c r="L14" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>540.4476382942248</v>
+      </c>
+      <c r="P14" t="n">
         <v>649</v>
-      </c>
-      <c r="N14" t="n">
-        <v>609.8778844919133</v>
-      </c>
-      <c r="O14" t="n">
-        <v>162.757678164601</v>
-      </c>
-      <c r="P14" t="n">
-        <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>397.807439363043</v>
       </c>
       <c r="N17" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -36080,7 +36080,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H19" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I19" t="n">
         <v>163.0214951995539</v>
@@ -36165,22 +36165,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
+        <v>648.9999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>560.5651175276444</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>649</v>
-      </c>
-      <c r="L20" t="n">
-        <v>649</v>
-      </c>
-      <c r="M20" t="n">
-        <v>649</v>
-      </c>
-      <c r="N20" t="n">
-        <v>179.1121759491994</v>
-      </c>
-      <c r="O20" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P20" t="n">
         <v>198.5777841804241</v>
@@ -36405,25 +36405,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K23" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L23" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M23" t="n">
         <v>649</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
+        <v>4.355038036034114</v>
+      </c>
+      <c r="O23" t="n">
         <v>649</v>
-      </c>
-      <c r="M23" t="n">
-        <v>179.1121759491996</v>
-      </c>
-      <c r="N23" t="n">
-        <v>649</v>
-      </c>
-      <c r="O23" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,19 +36642,19 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L26" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
         <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
-        <v>162.757678164601</v>
+        <v>596.7236430585247</v>
       </c>
       <c r="P26" t="n">
         <v>198.5777841804241</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L29" t="n">
-        <v>649</v>
+        <v>221.895519765053</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -37113,16 +37113,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L32" t="n">
-        <v>649.0000000000001</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
-        <v>221.8955197650528</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
         <v>649</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>179.1121759491994</v>
+        <v>649</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314919996</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37836,10 +37836,10 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>4.355038036034114</v>
+        <v>490.5973598714331</v>
       </c>
       <c r="O41" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
         <v>198.5777841804241</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M44" t="n">
         <v>649</v>
       </c>
-      <c r="M44" t="n">
-        <v>397.807439363043</v>
-      </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
